--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,1086 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121396620</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Romälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>479963</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6595503</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121396741</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79190</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Romälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>479943</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6595211</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121396659</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56555</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Romälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>479967</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6595448</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121396697</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90717</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Romälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>479983</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6595292</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121396671</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79190</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Romälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>479912</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6595385</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121396685</v>
+      </c>
+      <c r="B8" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Romälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>479955</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6595327</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121396634</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>53</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Romälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>479963</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6595436</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121396629</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Romälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>479959</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6595462</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121396706</v>
+      </c>
+      <c r="B11" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Romälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>480006</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6595244</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121396712</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78601</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Romälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>479950</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6595237</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121396620</v>
+        <v>121396697</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>90717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,24 +793,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -820,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479963</v>
+        <v>479983</v>
       </c>
       <c r="R3" t="n">
-        <v>6595503</v>
+        <v>6595292</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,6 +860,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396741</v>
+        <v>121396629</v>
       </c>
       <c r="B4" t="n">
-        <v>79190</v>
+        <v>90662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479943</v>
+        <v>479959</v>
       </c>
       <c r="R4" t="n">
-        <v>6595211</v>
+        <v>6595462</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396659</v>
+        <v>121396613</v>
       </c>
       <c r="B5" t="n">
-        <v>56555</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,35 +1014,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479967</v>
+        <v>479963</v>
       </c>
       <c r="R5" t="n">
-        <v>6595448</v>
+        <v>6595503</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,6 +1085,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396697</v>
+        <v>121396712</v>
       </c>
       <c r="B6" t="n">
-        <v>90717</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,28 +1120,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1150,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479983</v>
+        <v>479950</v>
       </c>
       <c r="R6" t="n">
-        <v>6595292</v>
+        <v>6595237</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,11 +1183,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396671</v>
+        <v>121396634</v>
       </c>
       <c r="B7" t="n">
-        <v>79190</v>
+        <v>95628</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,26 +1226,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1261,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479912</v>
+        <v>479963</v>
       </c>
       <c r="R7" t="n">
-        <v>6595385</v>
+        <v>6595436</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396685</v>
+        <v>121396659</v>
       </c>
       <c r="B8" t="n">
-        <v>95628</v>
+        <v>56555</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,27 +1333,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479955</v>
+        <v>479967</v>
       </c>
       <c r="R8" t="n">
-        <v>6595327</v>
+        <v>6595448</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,7 +1413,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396634</v>
+        <v>121396685</v>
       </c>
       <c r="B9" t="n">
         <v>95628</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479963</v>
+        <v>479955</v>
       </c>
       <c r="R9" t="n">
-        <v>6595436</v>
+        <v>6595327</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396629</v>
+        <v>121396663</v>
       </c>
       <c r="B10" t="n">
-        <v>90662</v>
+        <v>79190</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479959</v>
+        <v>479912</v>
       </c>
       <c r="R10" t="n">
-        <v>6595462</v>
+        <v>6595385</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396706</v>
+        <v>121396741</v>
       </c>
       <c r="B11" t="n">
-        <v>95628</v>
+        <v>79190</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,27 +1660,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1688,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480006</v>
+        <v>479943</v>
       </c>
       <c r="R11" t="n">
-        <v>6595244</v>
+        <v>6595211</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1751,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121396712</v>
+        <v>121396706</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>95628</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,26 +1766,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479950</v>
+        <v>480006</v>
       </c>
       <c r="R12" t="n">
-        <v>6595237</v>
+        <v>6595244</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121396697</v>
+        <v>121396671</v>
       </c>
       <c r="B3" t="n">
-        <v>90717</v>
+        <v>79190</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,28 +793,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -824,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479983</v>
+        <v>479912</v>
       </c>
       <c r="R3" t="n">
-        <v>6595292</v>
+        <v>6595385</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396629</v>
+        <v>121396634</v>
       </c>
       <c r="B4" t="n">
-        <v>90662</v>
+        <v>95628</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +895,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479959</v>
+        <v>479963</v>
       </c>
       <c r="R4" t="n">
-        <v>6595462</v>
+        <v>6595436</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1210,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396634</v>
+        <v>121396741</v>
       </c>
       <c r="B7" t="n">
-        <v>95628</v>
+        <v>79190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,27 +1218,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1254,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479963</v>
+        <v>479943</v>
       </c>
       <c r="R7" t="n">
-        <v>6595436</v>
+        <v>6595211</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396659</v>
+        <v>121396629</v>
       </c>
       <c r="B8" t="n">
-        <v>56555</v>
+        <v>90662</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,39 +1320,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1369,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479967</v>
+        <v>479959</v>
       </c>
       <c r="R8" t="n">
-        <v>6595448</v>
+        <v>6595462</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1413,6 +1395,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1431,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396685</v>
+        <v>121396706</v>
       </c>
       <c r="B9" t="n">
         <v>95628</v>
@@ -1475,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479955</v>
+        <v>480006</v>
       </c>
       <c r="R9" t="n">
-        <v>6595327</v>
+        <v>6595244</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396663</v>
+        <v>121396697</v>
       </c>
       <c r="B10" t="n">
-        <v>79190</v>
+        <v>90717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,24 +1537,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1581,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479912</v>
+        <v>479983</v>
       </c>
       <c r="R10" t="n">
-        <v>6595385</v>
+        <v>6595292</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1617,6 +1604,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396741</v>
+        <v>121396685</v>
       </c>
       <c r="B11" t="n">
-        <v>79190</v>
+        <v>95628</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,26 +1652,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1687,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479943</v>
+        <v>479955</v>
       </c>
       <c r="R11" t="n">
-        <v>6595211</v>
+        <v>6595327</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1750,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121396706</v>
+        <v>121396659</v>
       </c>
       <c r="B12" t="n">
-        <v>95628</v>
+        <v>56555</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,27 +1759,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1794,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480006</v>
+        <v>479967</v>
       </c>
       <c r="R12" t="n">
-        <v>6595244</v>
+        <v>6595448</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1838,7 +1839,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396685</v>
+        <v>121396659</v>
       </c>
       <c r="B11" t="n">
-        <v>95628</v>
+        <v>56555</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,27 +1652,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479955</v>
+        <v>479967</v>
       </c>
       <c r="R11" t="n">
-        <v>6595327</v>
+        <v>6595448</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1724,7 +1732,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1743,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121396659</v>
+        <v>121396685</v>
       </c>
       <c r="B12" t="n">
-        <v>56555</v>
+        <v>95628</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,35 +1766,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479967</v>
+        <v>479955</v>
       </c>
       <c r="R12" t="n">
-        <v>6595448</v>
+        <v>6595327</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1839,6 +1838,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121396671</v>
+        <v>121396741</v>
       </c>
       <c r="B3" t="n">
-        <v>79190</v>
+        <v>79193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479912</v>
+        <v>479943</v>
       </c>
       <c r="R3" t="n">
-        <v>6595385</v>
+        <v>6595211</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396634</v>
+        <v>121396613</v>
       </c>
       <c r="B4" t="n">
-        <v>95628</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,27 +899,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,7 +929,7 @@
         <v>479963</v>
       </c>
       <c r="R4" t="n">
-        <v>6595436</v>
+        <v>6595503</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396613</v>
+        <v>121396671</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>79193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479963</v>
+        <v>479912</v>
       </c>
       <c r="R5" t="n">
-        <v>6595503</v>
+        <v>6595385</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396712</v>
+        <v>121396706</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>95641</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,26 +1111,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479950</v>
+        <v>480006</v>
       </c>
       <c r="R6" t="n">
-        <v>6595237</v>
+        <v>6595244</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1202,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396741</v>
+        <v>121396685</v>
       </c>
       <c r="B7" t="n">
-        <v>79190</v>
+        <v>95641</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,26 +1218,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1245,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479943</v>
+        <v>479955</v>
       </c>
       <c r="R7" t="n">
-        <v>6595211</v>
+        <v>6595327</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,7 +1312,7 @@
         <v>121396629</v>
       </c>
       <c r="B8" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396706</v>
+        <v>121396712</v>
       </c>
       <c r="B9" t="n">
-        <v>95628</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,27 +1431,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480006</v>
+        <v>479950</v>
       </c>
       <c r="R9" t="n">
-        <v>6595244</v>
+        <v>6595237</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396697</v>
+        <v>121396634</v>
       </c>
       <c r="B10" t="n">
-        <v>90717</v>
+        <v>95641</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,30 +1537,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1568,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479983</v>
+        <v>479963</v>
       </c>
       <c r="R10" t="n">
-        <v>6595292</v>
+        <v>6595436</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1604,11 +1601,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396659</v>
+        <v>121396697</v>
       </c>
       <c r="B11" t="n">
-        <v>56555</v>
+        <v>90729</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,35 +1644,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1688,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479967</v>
+        <v>479983</v>
       </c>
       <c r="R11" t="n">
-        <v>6595448</v>
+        <v>6595292</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1726,12 +1713,18 @@
           <t>2024-11-29</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1750,14 +1743,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121396685</v>
+        <v>121396659</v>
       </c>
       <c r="B12" t="n">
-        <v>95628</v>
+        <v>56555</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1766,27 +1759,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1794,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479955</v>
+        <v>479967</v>
       </c>
       <c r="R12" t="n">
-        <v>6595327</v>
+        <v>6595448</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1838,7 +1839,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121396741</v>
+        <v>121396706</v>
       </c>
       <c r="B3" t="n">
-        <v>79193</v>
+        <v>95642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,26 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479943</v>
+        <v>480006</v>
       </c>
       <c r="R3" t="n">
-        <v>6595211</v>
+        <v>6595244</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396613</v>
+        <v>121396671</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>79193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479963</v>
+        <v>479912</v>
       </c>
       <c r="R4" t="n">
-        <v>6595503</v>
+        <v>6595385</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396671</v>
+        <v>121396629</v>
       </c>
       <c r="B5" t="n">
-        <v>79193</v>
+        <v>90675</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479912</v>
+        <v>479959</v>
       </c>
       <c r="R5" t="n">
-        <v>6595385</v>
+        <v>6595462</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396706</v>
+        <v>121396620</v>
       </c>
       <c r="B6" t="n">
-        <v>95641</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,27 +1112,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480006</v>
+        <v>479963</v>
       </c>
       <c r="R6" t="n">
-        <v>6595244</v>
+        <v>6595503</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1202,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396685</v>
+        <v>121396741</v>
       </c>
       <c r="B7" t="n">
-        <v>95641</v>
+        <v>79193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,27 +1218,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1246,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479955</v>
+        <v>479943</v>
       </c>
       <c r="R7" t="n">
-        <v>6595327</v>
+        <v>6595211</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1309,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396629</v>
+        <v>121396697</v>
       </c>
       <c r="B8" t="n">
-        <v>90674</v>
+        <v>90730</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,28 +1320,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1352,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479959</v>
+        <v>479983</v>
       </c>
       <c r="R8" t="n">
-        <v>6595462</v>
+        <v>6595292</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1388,6 +1391,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396712</v>
+        <v>121396634</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>95642</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,26 +1439,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1458,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479950</v>
+        <v>479963</v>
       </c>
       <c r="R9" t="n">
-        <v>6595237</v>
+        <v>6595436</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1521,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396634</v>
+        <v>121396712</v>
       </c>
       <c r="B10" t="n">
-        <v>95641</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,27 +1546,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1565,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479963</v>
+        <v>479950</v>
       </c>
       <c r="R10" t="n">
-        <v>6595436</v>
+        <v>6595237</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396697</v>
+        <v>121396685</v>
       </c>
       <c r="B11" t="n">
-        <v>90729</v>
+        <v>95642</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,30 +1652,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1675,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479983</v>
+        <v>479955</v>
       </c>
       <c r="R11" t="n">
-        <v>6595292</v>
+        <v>6595327</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1711,11 +1716,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>121396706</v>
       </c>
       <c r="B3" t="n">
-        <v>95642</v>
+        <v>95645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396671</v>
+        <v>121396620</v>
       </c>
       <c r="B4" t="n">
-        <v>79193</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479912</v>
+        <v>479963</v>
       </c>
       <c r="R4" t="n">
-        <v>6595385</v>
+        <v>6595503</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396629</v>
+        <v>121396697</v>
       </c>
       <c r="B5" t="n">
-        <v>90675</v>
+        <v>90733</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,28 +1002,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1033,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479959</v>
+        <v>479983</v>
       </c>
       <c r="R5" t="n">
-        <v>6595462</v>
+        <v>6595292</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1069,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396620</v>
+        <v>121396663</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>79196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479963</v>
+        <v>479912</v>
       </c>
       <c r="R6" t="n">
-        <v>6595503</v>
+        <v>6595385</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1202,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396741</v>
+        <v>121396634</v>
       </c>
       <c r="B7" t="n">
-        <v>79193</v>
+        <v>95645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,26 +1227,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1245,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479943</v>
+        <v>479963</v>
       </c>
       <c r="R7" t="n">
-        <v>6595211</v>
+        <v>6595436</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396697</v>
+        <v>121396629</v>
       </c>
       <c r="B8" t="n">
-        <v>90730</v>
+        <v>90678</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1320,32 +1330,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1355,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479983</v>
+        <v>479959</v>
       </c>
       <c r="R8" t="n">
-        <v>6595292</v>
+        <v>6595462</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1391,11 +1397,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396634</v>
+        <v>121396685</v>
       </c>
       <c r="B9" t="n">
-        <v>95642</v>
+        <v>95645</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479963</v>
+        <v>479955</v>
       </c>
       <c r="R9" t="n">
-        <v>6595436</v>
+        <v>6595327</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,7 +1534,7 @@
         <v>121396712</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396685</v>
+        <v>121396741</v>
       </c>
       <c r="B11" t="n">
-        <v>95642</v>
+        <v>79196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,27 +1653,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479955</v>
+        <v>479943</v>
       </c>
       <c r="R11" t="n">
-        <v>6595327</v>
+        <v>6595211</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1746,7 +1746,7 @@
         <v>121396659</v>
       </c>
       <c r="B12" t="n">
-        <v>56555</v>
+        <v>56558</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121396706</v>
+        <v>121396697</v>
       </c>
       <c r="B3" t="n">
-        <v>95645</v>
+        <v>90733</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,27 +793,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -821,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480006</v>
+        <v>479983</v>
       </c>
       <c r="R3" t="n">
-        <v>6595244</v>
+        <v>6595292</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,6 +860,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396620</v>
+        <v>121396629</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>90678</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479963</v>
+        <v>479959</v>
       </c>
       <c r="R4" t="n">
-        <v>6595503</v>
+        <v>6595462</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396697</v>
+        <v>121396706</v>
       </c>
       <c r="B5" t="n">
-        <v>90733</v>
+        <v>95645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,30 +1014,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479983</v>
+        <v>480006</v>
       </c>
       <c r="R5" t="n">
-        <v>6595292</v>
+        <v>6595244</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396663</v>
+        <v>121396712</v>
       </c>
       <c r="B6" t="n">
-        <v>79196</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479912</v>
+        <v>479950</v>
       </c>
       <c r="R6" t="n">
-        <v>6595385</v>
+        <v>6595237</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396629</v>
+        <v>121396741</v>
       </c>
       <c r="B8" t="n">
-        <v>90678</v>
+        <v>79196</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,25 +1330,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479959</v>
+        <v>479943</v>
       </c>
       <c r="R8" t="n">
-        <v>6595462</v>
+        <v>6595211</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396685</v>
+        <v>121396613</v>
       </c>
       <c r="B9" t="n">
-        <v>95645</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,27 +1440,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1468,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479955</v>
+        <v>479963</v>
       </c>
       <c r="R9" t="n">
-        <v>6595327</v>
+        <v>6595503</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1531,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396712</v>
+        <v>121396685</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>95645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,26 +1546,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479950</v>
+        <v>479955</v>
       </c>
       <c r="R10" t="n">
-        <v>6595237</v>
+        <v>6595327</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396741</v>
+        <v>121396671</v>
       </c>
       <c r="B11" t="n">
         <v>79196</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479943</v>
+        <v>479912</v>
       </c>
       <c r="R11" t="n">
-        <v>6595211</v>
+        <v>6595385</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121396697</v>
+        <v>121396629</v>
       </c>
       <c r="B3" t="n">
-        <v>90733</v>
+        <v>90684</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,32 +789,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -824,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479983</v>
+        <v>479959</v>
       </c>
       <c r="R3" t="n">
-        <v>6595292</v>
+        <v>6595462</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396629</v>
+        <v>121396706</v>
       </c>
       <c r="B4" t="n">
-        <v>90678</v>
+        <v>95651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +895,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479959</v>
+        <v>480006</v>
       </c>
       <c r="R4" t="n">
-        <v>6595462</v>
+        <v>6595244</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396706</v>
+        <v>121396634</v>
       </c>
       <c r="B5" t="n">
-        <v>95645</v>
+        <v>95651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480006</v>
+        <v>479963</v>
       </c>
       <c r="R5" t="n">
-        <v>6595244</v>
+        <v>6595436</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396712</v>
+        <v>121396620</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479950</v>
+        <v>479963</v>
       </c>
       <c r="R6" t="n">
-        <v>6595237</v>
+        <v>6595503</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1211,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396634</v>
+        <v>121396741</v>
       </c>
       <c r="B7" t="n">
-        <v>95645</v>
+        <v>79197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,27 +1219,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479963</v>
+        <v>479943</v>
       </c>
       <c r="R7" t="n">
-        <v>6595436</v>
+        <v>6595211</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1318,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396741</v>
+        <v>121396671</v>
       </c>
       <c r="B8" t="n">
-        <v>79196</v>
+        <v>79197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479943</v>
+        <v>479912</v>
       </c>
       <c r="R8" t="n">
-        <v>6595211</v>
+        <v>6595385</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396613</v>
+        <v>121396685</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>95651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,26 +1431,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1467,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479963</v>
+        <v>479955</v>
       </c>
       <c r="R9" t="n">
-        <v>6595503</v>
+        <v>6595327</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396685</v>
+        <v>121396697</v>
       </c>
       <c r="B10" t="n">
-        <v>95645</v>
+        <v>90739</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,27 +1538,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1574,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479955</v>
+        <v>479983</v>
       </c>
       <c r="R10" t="n">
-        <v>6595327</v>
+        <v>6595292</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1610,6 +1605,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396671</v>
+        <v>121396712</v>
       </c>
       <c r="B11" t="n">
-        <v>79196</v>
+        <v>78608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479912</v>
+        <v>479950</v>
       </c>
       <c r="R11" t="n">
-        <v>6595385</v>
+        <v>6595237</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1746,7 +1746,7 @@
         <v>121396659</v>
       </c>
       <c r="B12" t="n">
-        <v>56558</v>
+        <v>56559</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121396629</v>
+        <v>121396634</v>
       </c>
       <c r="B3" t="n">
-        <v>90684</v>
+        <v>95652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,30 +789,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479959</v>
+        <v>479963</v>
       </c>
       <c r="R3" t="n">
-        <v>6595462</v>
+        <v>6595436</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,7 +887,7 @@
         <v>121396706</v>
       </c>
       <c r="B4" t="n">
-        <v>95651</v>
+        <v>95652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -990,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396634</v>
+        <v>121396620</v>
       </c>
       <c r="B5" t="n">
-        <v>95651</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,27 +1007,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>479963</v>
       </c>
       <c r="R5" t="n">
-        <v>6595436</v>
+        <v>6595503</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396620</v>
+        <v>121396697</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>90740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,24 +1113,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1140,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479963</v>
+        <v>479983</v>
       </c>
       <c r="R6" t="n">
-        <v>6595503</v>
+        <v>6595292</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1176,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396741</v>
+        <v>121396712</v>
       </c>
       <c r="B7" t="n">
-        <v>79197</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479943</v>
+        <v>479950</v>
       </c>
       <c r="R7" t="n">
-        <v>6595211</v>
+        <v>6595237</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1309,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396671</v>
+        <v>121396741</v>
       </c>
       <c r="B8" t="n">
-        <v>79197</v>
+        <v>79198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479912</v>
+        <v>479943</v>
       </c>
       <c r="R8" t="n">
-        <v>6595385</v>
+        <v>6595211</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396685</v>
+        <v>121396629</v>
       </c>
       <c r="B9" t="n">
-        <v>95651</v>
+        <v>90685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,31 +1436,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1459,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479955</v>
+        <v>479959</v>
       </c>
       <c r="R9" t="n">
-        <v>6595327</v>
+        <v>6595462</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396697</v>
+        <v>121396685</v>
       </c>
       <c r="B10" t="n">
-        <v>90739</v>
+        <v>95652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,30 +1546,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1569,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479983</v>
+        <v>479955</v>
       </c>
       <c r="R10" t="n">
-        <v>6595292</v>
+        <v>6595327</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1605,11 +1610,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396712</v>
+        <v>121396663</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>79198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479950</v>
+        <v>479912</v>
       </c>
       <c r="R11" t="n">
-        <v>6595237</v>
+        <v>6595385</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1746,7 +1746,7 @@
         <v>121396659</v>
       </c>
       <c r="B12" t="n">
-        <v>56559</v>
+        <v>56560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121396634</v>
+        <v>121396697</v>
       </c>
       <c r="B3" t="n">
-        <v>95652</v>
+        <v>90740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,27 +793,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -821,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479963</v>
+        <v>479983</v>
       </c>
       <c r="R3" t="n">
-        <v>6595436</v>
+        <v>6595292</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,6 +860,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396706</v>
+        <v>121396613</v>
       </c>
       <c r="B4" t="n">
-        <v>95652</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,27 +908,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -928,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480006</v>
+        <v>479963</v>
       </c>
       <c r="R4" t="n">
-        <v>6595244</v>
+        <v>6595503</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396620</v>
+        <v>121396634</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>95652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,26 +1014,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,7 +1045,7 @@
         <v>479963</v>
       </c>
       <c r="R5" t="n">
-        <v>6595503</v>
+        <v>6595436</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396697</v>
+        <v>121396629</v>
       </c>
       <c r="B6" t="n">
-        <v>90740</v>
+        <v>90685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,32 +1117,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1144,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479983</v>
+        <v>479959</v>
       </c>
       <c r="R6" t="n">
-        <v>6595292</v>
+        <v>6595462</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1180,11 +1184,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396712</v>
+        <v>121396741</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,21 +1227,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479950</v>
+        <v>479943</v>
       </c>
       <c r="R7" t="n">
-        <v>6595237</v>
+        <v>6595211</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1318,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396741</v>
+        <v>121396671</v>
       </c>
       <c r="B8" t="n">
         <v>79198</v>
@@ -1361,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479943</v>
+        <v>479912</v>
       </c>
       <c r="R8" t="n">
-        <v>6595211</v>
+        <v>6595385</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396629</v>
+        <v>121396706</v>
       </c>
       <c r="B9" t="n">
-        <v>90685</v>
+        <v>95652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,30 +1435,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479959</v>
+        <v>480006</v>
       </c>
       <c r="R9" t="n">
-        <v>6595462</v>
+        <v>6595244</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396685</v>
+        <v>121396712</v>
       </c>
       <c r="B10" t="n">
-        <v>95652</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,27 +1546,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1574,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479955</v>
+        <v>479950</v>
       </c>
       <c r="R10" t="n">
-        <v>6595327</v>
+        <v>6595237</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396663</v>
+        <v>121396685</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>95652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,26 +1652,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479912</v>
+        <v>479955</v>
       </c>
       <c r="R11" t="n">
-        <v>6595385</v>
+        <v>6595327</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396613</v>
+        <v>121396663</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479963</v>
+        <v>479912</v>
       </c>
       <c r="R4" t="n">
-        <v>6595503</v>
+        <v>6595385</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396634</v>
+        <v>121396620</v>
       </c>
       <c r="B5" t="n">
-        <v>95652</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,27 +1014,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,7 +1044,7 @@
         <v>479963</v>
       </c>
       <c r="R5" t="n">
-        <v>6595436</v>
+        <v>6595503</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396629</v>
+        <v>121396634</v>
       </c>
       <c r="B6" t="n">
-        <v>90685</v>
+        <v>95652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,30 +1116,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479959</v>
+        <v>479963</v>
       </c>
       <c r="R6" t="n">
-        <v>6595462</v>
+        <v>6595436</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396741</v>
+        <v>121396706</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>95652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,26 +1227,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1254,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479943</v>
+        <v>480006</v>
       </c>
       <c r="R7" t="n">
-        <v>6595211</v>
+        <v>6595244</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396671</v>
+        <v>121396685</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>95652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,26 +1334,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1360,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479912</v>
+        <v>479955</v>
       </c>
       <c r="R8" t="n">
-        <v>6595385</v>
+        <v>6595327</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396706</v>
+        <v>121396741</v>
       </c>
       <c r="B9" t="n">
-        <v>95652</v>
+        <v>79198</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,27 +1441,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1467,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480006</v>
+        <v>479943</v>
       </c>
       <c r="R9" t="n">
-        <v>6595244</v>
+        <v>6595211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396712</v>
+        <v>121396629</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,25 +1543,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479950</v>
+        <v>479959</v>
       </c>
       <c r="R10" t="n">
-        <v>6595237</v>
+        <v>6595462</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1636,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396685</v>
+        <v>121396712</v>
       </c>
       <c r="B11" t="n">
-        <v>95652</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,27 +1653,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479955</v>
+        <v>479950</v>
       </c>
       <c r="R11" t="n">
-        <v>6595327</v>
+        <v>6595237</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121396697</v>
+        <v>121396706</v>
       </c>
       <c r="B3" t="n">
-        <v>90740</v>
+        <v>95652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479983</v>
+        <v>480006</v>
       </c>
       <c r="R3" t="n">
-        <v>6595292</v>
+        <v>6595244</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396663</v>
+        <v>121396741</v>
       </c>
       <c r="B4" t="n">
         <v>79198</v>
@@ -935,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479912</v>
+        <v>479943</v>
       </c>
       <c r="R4" t="n">
-        <v>6595385</v>
+        <v>6595211</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396620</v>
+        <v>121396613</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1104,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396634</v>
+        <v>121396629</v>
       </c>
       <c r="B6" t="n">
-        <v>95652</v>
+        <v>90685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,31 +1108,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1148,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479963</v>
+        <v>479959</v>
       </c>
       <c r="R6" t="n">
-        <v>6595436</v>
+        <v>6595462</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1211,7 +1202,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396706</v>
+        <v>121396685</v>
       </c>
       <c r="B7" t="n">
         <v>95652</v>
@@ -1255,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480006</v>
+        <v>479955</v>
       </c>
       <c r="R7" t="n">
-        <v>6595244</v>
+        <v>6595327</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1318,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396685</v>
+        <v>121396671</v>
       </c>
       <c r="B8" t="n">
-        <v>95652</v>
+        <v>79198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,27 +1325,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1362,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479955</v>
+        <v>479912</v>
       </c>
       <c r="R8" t="n">
-        <v>6595327</v>
+        <v>6595385</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1425,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396741</v>
+        <v>121396697</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>90740</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,24 +1431,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1468,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479943</v>
+        <v>479983</v>
       </c>
       <c r="R9" t="n">
-        <v>6595211</v>
+        <v>6595292</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,6 +1498,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396629</v>
+        <v>121396712</v>
       </c>
       <c r="B10" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,25 +1542,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479959</v>
+        <v>479950</v>
       </c>
       <c r="R10" t="n">
-        <v>6595462</v>
+        <v>6595237</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396712</v>
+        <v>121396634</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>95652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,26 +1652,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479950</v>
+        <v>479963</v>
       </c>
       <c r="R11" t="n">
-        <v>6595237</v>
+        <v>6595436</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 55770-2024 artfynd.xlsx
+++ b/artfynd/A 55770-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121396706</v>
+        <v>121396685</v>
       </c>
       <c r="B3" t="n">
-        <v>95652</v>
+        <v>95660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480006</v>
+        <v>479955</v>
       </c>
       <c r="R3" t="n">
-        <v>6595244</v>
+        <v>6595327</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121396741</v>
+        <v>121396620</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479943</v>
+        <v>479963</v>
       </c>
       <c r="R4" t="n">
-        <v>6595211</v>
+        <v>6595503</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121396613</v>
+        <v>121396634</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>95660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,26 +1006,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,7 +1037,7 @@
         <v>479963</v>
       </c>
       <c r="R5" t="n">
-        <v>6595503</v>
+        <v>6595436</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121396629</v>
+        <v>121396697</v>
       </c>
       <c r="B6" t="n">
-        <v>90685</v>
+        <v>90748</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,28 +1109,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479959</v>
+        <v>479983</v>
       </c>
       <c r="R6" t="n">
-        <v>6595462</v>
+        <v>6595292</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121396685</v>
+        <v>121396663</v>
       </c>
       <c r="B7" t="n">
-        <v>95652</v>
+        <v>79205</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,27 +1228,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1246,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479955</v>
+        <v>479912</v>
       </c>
       <c r="R7" t="n">
-        <v>6595327</v>
+        <v>6595385</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1309,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121396671</v>
+        <v>121396629</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>90693</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,25 +1330,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479912</v>
+        <v>479959</v>
       </c>
       <c r="R8" t="n">
-        <v>6595385</v>
+        <v>6595462</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121396697</v>
+        <v>121396706</v>
       </c>
       <c r="B9" t="n">
-        <v>90740</v>
+        <v>95660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,30 +1440,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1462,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479983</v>
+        <v>480006</v>
       </c>
       <c r="R9" t="n">
-        <v>6595292</v>
+        <v>6595244</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1498,11 +1504,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gammeltall med spillkråkehål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121396712</v>
+        <v>121396741</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>79205</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479950</v>
+        <v>479943</v>
       </c>
       <c r="R10" t="n">
-        <v>6595237</v>
+        <v>6595211</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1636,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121396634</v>
+        <v>121396712</v>
       </c>
       <c r="B11" t="n">
-        <v>95652</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,27 +1653,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479963</v>
+        <v>479950</v>
       </c>
       <c r="R11" t="n">
-        <v>6595436</v>
+        <v>6595237</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1746,7 +1746,7 @@
         <v>121396659</v>
       </c>
       <c r="B12" t="n">
-        <v>56560</v>
+        <v>56561</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
